--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99320</v>
+        <v>99323</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99323</v>
+        <v>99324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 56024-2025 artfynd.xlsx
+++ b/artfynd/A 56024-2025 artfynd.xlsx
@@ -5081,7 +5081,7 @@
         <v>136153629</v>
       </c>
       <c r="B38" t="n">
-        <v>99324</v>
+        <v>99329</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
